--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
@@ -708,7 +708,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -717,10 +717,10 @@
         <v>5</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>73.53</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H5">
         <v>7.7</v>
@@ -734,7 +734,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -743,10 +743,10 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>82.05</v>
+        <v>82.5</v>
       </c>
       <c r="H6">
         <v>7.1</v>
@@ -969,13 +969,13 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -992,13 +992,13 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1227,10 +1227,10 @@
         <v>9</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>73.53</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H5">
         <v>7.4</v>
@@ -1244,7 +1244,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1253,10 +1253,10 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>82.05</v>
+        <v>82.5</v>
       </c>
       <c r="H6">
         <v>7.2</v>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -94,148 +94,82 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MONTERD</t>
-  </si>
-  <si>
-    <t>TELLO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
+    <t>ECHAVARRIA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>SOSA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
+    <t>DURAND</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TETLA</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>CARPINTEYRO</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>MANZANO</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>JUAN YAHEL</t>
-  </si>
-  <si>
-    <t>ANGEL YAMIL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSE GUADALUPE</t>
-  </si>
-  <si>
-    <t>IVONNE ERIMAR</t>
-  </si>
-  <si>
-    <t>MARIEL BIDEMI</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>ANGEL URIEL</t>
-  </si>
-  <si>
-    <t>LEYLA SARAI</t>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>IAN</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>DIANA ARLET</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>HECTOR</t>
   </si>
   <si>
     <t>ANDRES</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>JOSUE YAHIR</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
   </si>
   <si>
     <t>MELANIE SOFIA</t>
@@ -708,7 +642,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -717,10 +651,10 @@
         <v>5</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>74.29000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="H5">
         <v>7.7</v>
@@ -792,13 +726,13 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>43.33</v>
+        <v>46.67</v>
       </c>
       <c r="H8">
         <v>6.2</v>
@@ -906,16 +840,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H2">
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -949,16 +886,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>45.83</v>
+      </c>
+      <c r="H4">
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -969,19 +909,22 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>76.47</v>
+      </c>
+      <c r="H5">
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -995,16 +938,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1018,16 +964,19 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>79.48999999999999</v>
+      </c>
+      <c r="H7">
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1041,16 +990,19 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>73.33</v>
+      </c>
+      <c r="H8">
+        <v>6.3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1064,16 +1016,19 @@
         <v>42</v>
       </c>
       <c r="D9">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H9">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1087,16 +1042,19 @@
         <v>43</v>
       </c>
       <c r="D10">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="H10">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1152,16 +1110,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>55.56</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1207,7 +1165,7 @@
         <v>45.83</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1218,22 +1176,22 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>26</v>
       </c>
       <c r="G5">
-        <v>74.29000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1250,16 +1208,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>82.5</v>
+        <v>87.5</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1276,16 +1234,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>66.67</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1302,16 +1260,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G8">
-        <v>43.33</v>
+        <v>73.33</v>
       </c>
       <c r="H8">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1328,16 +1286,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9">
-        <v>90.48</v>
+        <v>92.86</v>
       </c>
       <c r="H9">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1354,16 +1312,16 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F10">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G10">
-        <v>69.77</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H10">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -1373,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1405,22 +1363,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920015</v>
+        <v>23330051920033</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1428,22 +1386,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920017</v>
+        <v>23330051920043</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" t="s">
-        <v>57</v>
-      </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1451,22 +1409,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920022</v>
+        <v>23330051920118</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
         <v>44</v>
       </c>
-      <c r="D4" t="s">
-        <v>58</v>
-      </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1474,22 +1432,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920030</v>
+        <v>23330051920123</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" t="s">
-        <v>59</v>
-      </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1497,22 +1455,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920071</v>
+        <v>22330051920054</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1520,22 +1478,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920074</v>
+        <v>22330051920068</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1543,22 +1501,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920082</v>
+        <v>22330051920084</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1566,277 +1524,70 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920097</v>
+        <v>23330051920160</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920124</v>
+        <v>22330051920116</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920315</v>
+        <v>22330051920079</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920146</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920105</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920116</v>
-      </c>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920054</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920068</v>
-      </c>
-      <c r="B16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920023</v>
-      </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920059</v>
-      </c>
-      <c r="B18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920061</v>
-      </c>
-      <c r="B19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920079</v>
-      </c>
-      <c r="B20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="49">
   <si>
     <t>Mat</t>
   </si>
@@ -94,9 +94,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ECHAVARRIA</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -106,6 +103,9 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -115,21 +115,18 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>DURAND</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
     <t>SOTO</t>
   </si>
   <si>
+    <t>TETLA</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
@@ -139,15 +136,9 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>TETLA</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
     <t>IAN</t>
   </si>
   <si>
@@ -157,6 +148,9 @@
     <t>DIANA ARLET</t>
   </si>
   <si>
+    <t>HECTOR</t>
+  </si>
+  <si>
     <t>FATIMA</t>
   </si>
   <si>
@@ -164,9 +158,6 @@
   </si>
   <si>
     <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>HECTOR</t>
   </si>
   <si>
     <t>ANDRES</t>
@@ -1331,7 +1322,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1363,16 +1354,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920033</v>
+        <v>23330051920043</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1386,22 +1377,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920043</v>
+        <v>23330051920118</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1409,16 +1400,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920118</v>
+        <v>23330051920123</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1432,22 +1423,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920123</v>
+        <v>23330051920160</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1461,10 +1452,10 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1484,10 +1475,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -1507,10 +1498,10 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1524,22 +1515,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920160</v>
+        <v>22330051920116</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1547,47 +1538,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920116</v>
+        <v>22330051920079</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920079</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,9 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>BAROJAS</t>
   </si>
   <si>
@@ -121,6 +124,9 @@
     <t>SOLANO</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>SOTO</t>
   </si>
   <si>
@@ -140,6 +146,9 @@
   </si>
   <si>
     <t>IAN</t>
+  </si>
+  <si>
+    <t>HUGO ISAI</t>
   </si>
   <si>
     <t>ANGEL DANIEL</t>
@@ -1322,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1360,10 +1369,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1377,22 +1386,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920118</v>
+        <v>23330051920052</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1400,16 +1409,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920123</v>
+        <v>23330051920118</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1423,22 +1432,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920160</v>
+        <v>23330051920123</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1446,22 +1455,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920054</v>
+        <v>23330051920160</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1469,16 +1478,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920068</v>
+        <v>22330051920054</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -1492,16 +1501,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920084</v>
+        <v>22330051920068</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1515,47 +1524,70 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920116</v>
+        <v>22330051920084</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920079</v>
+        <v>22330051920116</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920079</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
         <v>18</v>
       </c>
-      <c r="G10">
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="67">
   <si>
     <t>Mat</t>
   </si>
@@ -94,85 +94,130 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>VELUETA</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>ABREGO</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>ZGAIP</t>
   </si>
   <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>SOTO</t>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
   </si>
   <si>
     <t>TETLA</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>IAN</t>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>ANGEL YAMIL</t>
+  </si>
+  <si>
+    <t>JOSE GUADALUPE</t>
   </si>
   <si>
     <t>HUGO ISAI</t>
   </si>
   <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>DIANA ARLET</t>
+    <t>MARY CELESTE</t>
+  </si>
+  <si>
+    <t>KEVIN IVAN</t>
+  </si>
+  <si>
+    <t>DANNAE ADALID</t>
+  </si>
+  <si>
+    <t>LUIS AARON</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>HERSON</t>
+  </si>
+  <si>
+    <t>SULU ALAN</t>
   </si>
   <si>
     <t>HECTOR</t>
   </si>
   <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>ADAIR DE JESUS</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -726,16 +771,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="H8">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1110,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1156,16 +1201,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>45.83</v>
+        <v>66.67</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1182,13 +1227,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>76.47</v>
+        <v>79.41</v>
       </c>
       <c r="H5">
         <v>7.6</v>
@@ -1208,13 +1253,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>87.5</v>
+        <v>92.5</v>
       </c>
       <c r="H6">
         <v>7.8</v>
@@ -1234,16 +1279,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>79.48999999999999</v>
+        <v>82.05</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1260,16 +1305,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>73.33</v>
+        <v>70</v>
       </c>
       <c r="H8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1286,16 +1331,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G9">
-        <v>92.86</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1312,16 +1357,16 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G10">
-        <v>81.40000000000001</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -1331,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1363,22 +1408,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920043</v>
+        <v>23330051920017</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1386,22 +1431,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920052</v>
+        <v>23330051920030</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1409,22 +1454,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920118</v>
+        <v>23330051920052</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1432,22 +1477,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920123</v>
+        <v>23330051920351</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1455,16 +1500,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920160</v>
+        <v>23330051920162</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1478,22 +1523,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920054</v>
+        <v>23330051920175</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1501,22 +1546,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920068</v>
+        <v>23330051920313</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1524,16 +1569,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920084</v>
+        <v>22330051920079</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -1547,47 +1592,162 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920116</v>
+        <v>22330051920084</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920079</v>
+        <v>23330051920016</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920151</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920160</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920164</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920176</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920317</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" t="s">
         <v>51</v>
       </c>
-      <c r="E11" t="s">
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s">
         <v>10</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F16" t="s">
         <v>18</v>
       </c>
-      <c r="G11">
+      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
@@ -641,16 +641,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="G3">
+        <v>85.19</v>
+      </c>
+      <c r="H3">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -908,16 +914,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="G3">
+        <v>85.19</v>
+      </c>
+      <c r="H3">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1175,16 +1187,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="G3">
+        <v>85.19</v>
+      </c>
+      <c r="H3">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
@@ -1176,7 +1176,7 @@
         <v>74.06999999999999</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1228,7 +1228,7 @@
         <v>66.67</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1254,7 +1254,7 @@
         <v>79.41</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1280,7 +1280,7 @@
         <v>92.5</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1306,7 +1306,7 @@
         <v>82.05</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1332,7 +1332,7 @@
         <v>70</v>
       </c>
       <c r="H8">
-        <v>6.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1358,7 +1358,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>8.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1384,7 +1384,7 @@
         <v>79.06999999999999</v>
       </c>
       <c r="H10">
-        <v>7.6</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20231.xlsx
@@ -1176,7 +1176,7 @@
         <v>74.06999999999999</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1228,7 +1228,7 @@
         <v>66.67</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1254,7 +1254,7 @@
         <v>79.41</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1280,7 +1280,7 @@
         <v>92.5</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1306,7 +1306,7 @@
         <v>82.05</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1332,7 +1332,7 @@
         <v>70</v>
       </c>
       <c r="H8">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1358,7 +1358,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1384,7 +1384,7 @@
         <v>79.06999999999999</v>
       </c>
       <c r="H10">
-        <v>9</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
